--- a/excel_ai/legacy/Tracking issues.xlsx
+++ b/excel_ai/legacy/Tracking issues.xlsx
@@ -10,9 +10,10 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01CA5EA-78FE-4C6E-8AB2-4F84478AB29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{39055DA2-BF7E-4A30-86A0-0114139A7EB4}"/>
+    <workbookView activeTab="0" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{39055DA2-BF7E-4A30-86A0-0114139A7EB4}"/>
   </bookViews>
   <sheets>
+    <sheet name="CPAT-AI_bugs" sheetId="7" r:id="rId14"/>
     <sheet name="CPAT_issues" sheetId="1" r:id="rId1"/>
     <sheet name="CPAT-MT" sheetId="3" r:id="rId2"/>
     <sheet name="Mit+Disn_DeepDive" sheetId="6" r:id="rId3"/>
@@ -4408,6 +4409,7341 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF1F4E78"/>
+  </sheetPr>
+  <dimension ref="A1:I166"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="8.9" customWidth="1"/>
+    <col min="2" max="2" width="71" customWidth="1"/>
+    <col min="3" max="3" width="17.9" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11.3" customWidth="1"/>
+    <col min="7" max="7" width="14.6" customWidth="1"/>
+    <col min="8" max="8" width="20.7" customWidth="1"/>
+    <col min="9" max="9" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Issues</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT Version with identified issue</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materiality/Priority</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Issue raised by</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Issue solved by</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Additional comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Services electricity demand grows with the industrial multiple after 2023</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-11</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation H3, row 3731.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autonomous efficiency gains use the efficiency elasticity instead of the usage elasticity</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation H1, rows 3691, 3697, 3703, 3709.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Income factor on the GDP elasticity applied twice and anchored to 2023</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation H1, rows 3692-3710.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Long-term storage cost allocation (33%) applied twice</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation J1, rows 3911 and 3912.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investment spending uses the capital cost at time factor 1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation L20, rows 4276-4284.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investment logit normalised by the cheapest type, including types that may not be built</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation L1/L4, rows 4046, 4073-4081.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Early coal retirement mixes nameplate and effective capacity</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation K4, row 3973.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effective coal retirement is not capped like the nameplate retirement</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation K5/K6, rows 3994, 4009-4011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feebate rebate per kWh consumed is added to the cost per kWh generated</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation D6, rows 3407-3409.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacity needed is computed from last year's plan, not from actual capacity</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation K7, row 4024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stray reference in dispatch</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): exactly the planned fix (the $G4291 term is gone). Where: Mitigation rows 3773, 3779 (I1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total nameplate investment row is zero</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 4273 (L19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other oil products: hardcoded pass-through 1 and margin 0</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H14" s="0"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation price block (other oil products). Fix: Take pass-through and margin of other oil products from the IMF price dataset, like the other oil products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass-through applied twice in the first projected year</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H15" s="0"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation txo rows (cs). Fix: Apply (1 - pass-through) once in the first projected year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETS: hardcoded relative price 1.1</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H16" s="0"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 1843. Fix: Use the volatility inputs of the ETS+LTS table instead of the fixed 1.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETS quick estimate linear in the semi-elasticity</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: log form in L1868 only; M1868:P1868 are still the constant 0 (plan: fill L1868:AE1868); Q onward is the L57 formula. Where: Mitigation row 1868. Fix: Use the log form: price = LN(cap / baseline) / (semi-elasticity x effectiveness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L18</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-energy methane never changes</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H18" s="0"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 6158-6213 (livestock, rice, waste). Fix: Grow livestock, rice and waste methane with their drivers (income, population) and apply the abatement shares already computed in rows 6168, 6180, 6192.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L19</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flaring CO2 counted as methane</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H19" s="0"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 6141-6142. Fix: Report the CO2 from flaring as CO2 in energy, not divided by the CH4 GWP in the CH4 row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L20</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population growth path</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H20" s="0"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 481, 2428 (macro drivers). Fix: Use the UN WPP population of sheet UNPop (or fix the growth path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L21</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waste abated with the livestock curve</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H21" s="0"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 6192. Fix: Use the waste curve of CH4Inputs for waste (row 6192 now = M6168, the livestock share).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L22</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigation missing from the local pollutant totals</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H22" s="0"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation local pollutant totals (sections 13-14). Fix: Add domestic navigation to the transport and total pollutant rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L23</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Services and food &amp; forestry missing from the pollutant totals</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H23" s="0"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 6690, 6792, ... (total emissions of each pollutant). Fix: Add services and food &amp; forestry to the total of each pollutant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L24</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GDP effect added to GDP growth every year</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H24" s="0"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2443-2446, 8274. Fix: Raise the GDP level by the effect: growth = (1 + g) x (1 + e(t-1)) / (1 + e(t-2)) - 1, not g + e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L25</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: distance tax and 2-3 wheeler EV subsidy apply in the baseline</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H25" s="0"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4451, 4720 (engineer road model, survey B1). Fix: Scenario number &gt; 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L26</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: freight and 2-3 wheeler income growth read coal subsidies from 2038</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H26" s="0"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4487 AB:AE (also 4501) (engineer road model, survey B2). Fix: Lagged GDP growth (row 2446) in all years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L27</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: vehicle ownership calibration only scales up (and uses 2024)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H27" s="0"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows H4787:J4787, H4903:J4903 (engineer road model, survey B3). Fix: Actual/expected in both directions at the last data year found in the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L28</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: freight-share cap and 2-3 wheeler peak use 2024</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H28" s="0"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows $N2168, J2169 (engineer road model, survey B3b). Fix: Last data year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L29</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: ownership of cars and trucks cannot fall</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H29" s="0"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows T4328, U4328 (engineer road model, survey B4). Fix: Allow a decrease of up to own_decline_fix a year (legacy 2-3 wheeler value, 10%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L30</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: bus fuel scaled by the wrong rows</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H30" s="0"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 5310-5314, 5318 (engineer road model, survey B6). Fix: Passenger fuel use by fuel in ktoe (5195-5198) and passenger electricity (5223), base bus energy in ktoe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L31</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: bus share grossed up as x(1+share)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H31" s="0"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows O5171:O5173 (engineer road model, survey B6b). Fix: /(1-bus share).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L32</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: industry emission factors for road diesel and LPG</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H32" s="0"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows G4376-G4378, G4419-G4421 (engineer road model, survey B7). Fix: Road EFs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L33</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: wrong elasticities and rows in freight and 2-3 wheeler distance</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H33" s="0"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows M5261, M5295, M5232, M4646 (engineer road model, survey B8). Fix: As the sibling rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L34</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: freight discounted at the power-sector WACC</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H34" s="0"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows K4329 (engineer road model, survey B8w). Fix: The consumer discount rate (row 4531).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L35</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: negative PHEV sales share</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H35" s="0"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4850 L:O (engineer road model, survey B9). Fix: (EV - BEV passenger share) x passenger share, ICE shares scaled to the rest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L36</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: charging-station subsidy ramp</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H36" s="0"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4343 (engineer road model, survey B10). Fix: 0 before the start year, linear to the target level, then constant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L37</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: new BEV maintenance at the ICEV rate</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H37" s="0"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4573 (engineer road model, survey B19). Fix: EV maintenance (J4328).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L38</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: used ICEV and BEV depreciation over different periods</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H38" s="0"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4598 (engineer road model, survey B20). Fix: Used ownership period - 1 (J4323-1) for both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L39</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: freight distance output omits LPG and LNG trucks</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H39" s="0"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 5267 (engineer road model, survey B21). Fix: All fuels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L40</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: wrong rows in average gas and EV fuel economy</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H40" s="0"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 5368, 5373 (engineer road model, survey B22). Fix: Right rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L41</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road: PHEVs carry the full BEV range anxiety</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-14</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H41" s="0"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 4555 (engineer road model, survey B23). Fix: No range anxiety for PHEVs (they refuel with gasoline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L42</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domestic aviation: GDP growth and shock swapped</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 5483-5492.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L43</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other energy use: no GDP growth</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H43" s="0"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 6063-6071. Fix: Point the income factor to row 2433 and add the additional-efficiency term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L44</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residential other oil products priced at the biomass price</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 5559.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L45</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residential leakage to biomass inconsistent</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: 10 of 12 planned cells fixed; M5588:AE5588 (change in kerosene) is unchanged (still $C5591 and the LPG share row 5582, plan: =-L5566*M5589*$E$1785) and M5590 is =M5589 (a percent change), not =M5588 (the energy change), so the kerosene equivalent biomass M5591 is in the wrong units. Where: Mitigation rows 5574-5593. Fix: Subtract the fossil change once, use the kerosene rows for kerosene, conserve the substituted energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L46</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road other biofuels: wrong price and terms</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 5406.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L47</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Self-generated renewables in aviation and navigation take the shock from wrong rows</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 5491, 5516.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L48</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residential initially-exempt rows: no income factor; starred "Yes*" exemption test</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 5546-5547, 5568-5570.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L49</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance of payments: oil without the share traded</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H49" s="0"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18162-18166, 742. Fix: Multiply the oil change in use by the share traded of row 742, as for gas and coal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L50</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance of payments: current account #NAME?, column lag, sign</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H50" s="0"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18180-18198. Fix: Read the WEO current account (BCA), drop the one-column lag and check the sign of policy net imports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L51</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy trade balance of coal valued at the oil price</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H51" s="0"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 743. Fix: Value the coal trade balance at the coal price (row 732), not the oil price (row 731).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L52</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewables take the world power parameters, never the country ones</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 2981-2985 P:T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L53</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual capacity factors are never used</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 2999-3007 N, Q, W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L54</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hydro investment always starts in the first year</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 4067 H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L55</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China, Japan and Korea take regional power data</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 2977-2985 K (Power A25:A356).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L56</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Countries without CoC risk data get Sri Lanka's WACC parameters</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: still Sri Lanka, now an explicit Default row 198 (=row 172); no flag, as the user noted. Where: CoC rows 202-390 D:V. Fix: Flag countries without CoC fixed data instead of using Sri Lanka.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L57</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New ETS: the quick price estimate is linear in the semi-elasticity</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): log form as planned, plus a guard for a zero semi-elasticity. Where: Mitigation ETS block (quick estimate, override row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L58</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local pollutants: subsectors without a GAINS match get zero factors</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H58" s="0"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 15885-16685 (GAINS factor lookups). Fix: Map subsectors without a GAINS match to the nearest GAINS subsector (services as residential, rail as road, industry as manufacturing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L59</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local pollutants and combustion CH4: fuels without a GAINS factor emit nothing</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H59" s="0"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 15885-16685 (GAINS factor lookups; sheet EF_PM). Fix: Give a fuel without a GAINS factor the nearest GAINS match (LPG: natural gas of the same subsector; food &amp; forestry: construction; else manufacturing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L60</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAT payment on oil products divided by the full VAT rate</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H60" s="0"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2595, 2618, 2641, 2664 (VAT payment). Fix: VAT payment = (supply cost + taxes) x VAT rate x household share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L61</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EU ETS price grows with the carbon-tax growth</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 1695 (from the column after the last data year).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L62</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing carbon tax on transport diesel, LPG and kerosene uses the rate row as coverage</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H62" s="0"/>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marked fixed by the CPAT team, but not fixed in legacy 465: L1760:AE1762 are unchanged from 456 (still rate x rate x coverage). Where: Mitigation rows 1760-1762. Fix: Take the fuel coverage row, and the single-price flag, for transport diesel, LPG and kerosene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L63</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing carbon tax fuel coverage: lookup range cut short</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H63" s="0"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marked fixed by the CPAT team, but not fixed in legacy 465: J1741:J1749 still MATCH on ECP!$E$133:$E$403, while the ECP block still runs to row 425 (Ukraine, Uruguay, United Kingdom miss out). Where: Mitigation J1741-J1749 (ECP!E133:E403). Fix: Look the fuel coverage up in the whole ECP block (to row 425).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L64</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No existing ETS on other oil products outside power</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 1711-1723.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L65</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carbon tax complementary to an existing ETS: last year's ETS coverage</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 2270-2288.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L66</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other energy use: no additional policy efficiency gains on fossil fuels</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H66" s="0"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows of other energy use (fossil fuels; renewables use $M2201). Fix: Add the industrial additional efficiency to the fossil rows of other energy use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L67</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power: capacity bought for this year's demand, although it comes online next year</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 4022-4031 (K7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L68</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GDP effects: the multiplier of lag 1 acts in the impulse year</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H68" s="0"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 8253-8274 (policy 14569-14590). Fix: Apply multiplier(t - s) to the impulse of year s (lag 0 in the impulse year), as the multiplier notes define the lags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L69</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GDP effects: the first cohort's excise drag is lost</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H69" s="0"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 8057 (policy 14373). Fix: Match the first cohort's excise use on its own row (L14372, baseline L8056), not L$8113.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L70</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue: industry gas excise uses the coal rate and coal use</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H70" s="0"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 7747 (policy 14063). Fix: Use the gas industry excise rate (row 2581) and gas industry use in row 7747.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L71</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue: biomass taxes, subsidies and VAT divided by the unit conversion</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H71" s="0"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 7791, 7805, 7859. Fix: Multiply by _conv_ktoe_to_gj in rows 7791, 7805, 7859.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L72</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue: next-year references</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F72" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H72" s="0"/>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 7657, 7742. Fix: Read column R (the year) in rows 7657 and 7742.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L73</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue: wrong coverage shares</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H73" s="0"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 7677 (policy 13993), 7704. Fix: Divide by the industry gas total (6428) in row 7677; use power x kerosene coverage (R2265 x R2270) in row 7704.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L75</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revenue reports: hard-coded row and mixed totals</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F74" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H74" s="0"/>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 17145-17149, 17175, 17186. Fix: Index the excise report by the matched row instead of 759; take electricity from rev.new in the revenue by fuel report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L76</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multipliers: empty CIT table, WAGE on the GNFS table, approximate country match, default to Estimated</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H75" s="0"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Multipliers rows 19-22, 38-45, 1624-1822. Fix: Point CIT to the labour-tax or an own table (or the income group), WAGE to its own table, MATCH the country exactly (0), default unknown text to the income group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L77</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Average prices: index rows point at the wrong rows, gas test on the policy total</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H76" s="0"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 16302, 16374-16390. Fix: Point rows 16383-16390 to the average-price rows of each fuel; test the baseline gas total in E16302; relabel "baseline = 100".</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L78</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETS: auctioned share drops to 0 after the target year unless "Constant"</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F77" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 1863 (MTInputs row 92).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L79</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETS: industry and transport priced as a whole when one subsector is covered</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F78" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H78" s="0"/>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2322-2325 (policy 8638-8641), 7775-7778. Fix: Price and charge the ETS by subsector coverage, not MAX over the sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L80</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETS: the carbon-tax trajectory rescaled when the ETS is on</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 2191, 2251.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L81</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consumer subsidy phase-out: the fixed subsidy takes last year's factor</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H80" s="0"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2460, 2483, 2506, ... 2598, ... 2713 (fixed portion of subsidy, each price block). Fix: Use the factor of the same column in the fixed-subsidy rows (Q2214 for Q).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L82</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residential gas producer subsidy reads the oil row</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H81" s="0"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 2547. Fix: Point row 2547 to row 826 (gas producer subsidy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L83</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electricity producer subsidy compounds the factor and lags a year</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): all three cells as planned. Where: Mitigation rows 3592, 3601, 3630.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L84</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electricity consumer subsidy phased with the price-control factor; option text mismatch</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: the formulas are fixed (O2214); the option text MTInputs!C138 still reads “Exempt/Include*” (plan: “DoNotPhaseOut*/Include”). Where: Mitigation rows 3606, 3635; MTInputs row 138. Fix: Phase the electricity consumer subsidy with the consumer factor (row 2214); one option text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L85</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electricity consumer subsidy info row subtracts industry</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H84" s="0"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 7806. Fix: Add the industry part: -(MIN(0, res) + MIN(0, ind)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L86</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No manual override for the electricity producer subsidy</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F85" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation I828.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L87</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulations never act: share 0 and the adjustments unused</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (High)</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: C2371 fixed as planned; I2403:I2419 (and policy I8719:I8735) dropped the E2189="Yes" condition as well as adding *$F$90: the share now applies whether or not that switch is on; check this is intended. Where: Mitigation C2371, F86:F90 (MTInputs rows 247-251). Fix: Set the regulation share (C2371) to the scenario's adjustment of MTInputs rows 247-250 (F86:F89) and use row 251 for feebates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L88</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulations never reach power</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F87" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 3398 ff..</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L89</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coal in road, residential and services reads the residential coal shadow price</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F88" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 5396, 5553, 5634.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L90</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residential leakage breaks the useful-energy balance</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F89" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): fixed in the L45 form (=-(M5578+M5584+M5591)), which the plan says covers L90. Where: Mitigation row 5593.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L91</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exempt residential fuel still leaks to biomass</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F90" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 5580, 5586 (against 5546-5547).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L92</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExemptMostCook never reaches Mitigation</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H91" s="0"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation I1784, K1795, rows 5568-5570. Fix: I1784 = IF(LEFT(H1784,3)="Yes",1,0); start rows 5568-5570 from L(total) x K1795.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L93</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuel coverage rows test text labels and contain #REF!</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F92" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 2259-2268 (column E).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L94</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exemption phase-in rules differ between rows</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H93" s="0"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2259-2265, 2270-2288 against 2266-2268, 5568-5570. Fix: One rule: MAX(MIN((t+1-YearPha)/ExemptPhaseoutPeriod,1),0) x ExemptPhaseout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L95</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power demand: efficiency increment sits on the net-exports row</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F94" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: rows 3691-3709 and 2827, 2828, 2834 read M2198 and row 3719 was cleared, but P2823:AE2823 (total power demand) and M2836:AE2836 (direct rebound) still read $M3719, now empty, so the additional power-demand efficiency drops out of those rows (same in the policy block, $M10035); point them at $M2198. Where: Mitigation row 3719 (D3719 = D3742 'Net Exports (Imports negative)', F:J net-export data egy.mit.nxp.ecy; L3719 'Additional Efficiency Improvements - Power demand', M3719 = M2198 = MTInputs F242); read as $M3719 in rows 3691, 3697, 3703, 3709. Fix: Put the efficiency increment on its own labelled row (or read M2198 directly); leave row 3719 to net exports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L96</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuel-use block: mislabelled parameter and fuel rows</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H95" s="0"/>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation C2199:C2201 ('Tax in nominal or real terms?', 'Exponential option or linear' twice) beside K2199:M2201 (road, residential, industrial additional efficiency, MTInputs F243-F245); E2385 (LPG 'Road'), E2386 (kerosene 'Industry') on all-sector rows (codes shp.lpg.all, shp.ker.all); D5615, D5711, D6058, D6069 'Other oil pinducts'. Fix: Give the additional-efficiency increments their own labelled rows; label the LPG and kerosene shadow-price rows 'All'; correct the typo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L97</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron &amp; steel memo rows unused; one reads next year's growth</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H96" s="0"/>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 5667-5676, 5703, 5727-5728 (iron &amp; steel block; M5667 = N2446). Fix: Delete the memo rows (or move them to a diagnostics area with the year's own growth M2446).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L98</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feebate inclusion of industry reads the ETS industry flag</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Manual inputs P54:X54 (name FeebateInclusion -&gt; MTInputs E66:E82).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L99</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETS inclusion of machinery and other manufacturing uses the buildings flag</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F98" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Manual inputs S11, U11 (name ETSInclusion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L100</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual domestic prices: the electricity rows are never read</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Manual inputs G59:N146 (names _manual_prices, _manual_codes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L101</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual services income elasticities read the industries column</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H100" s="0"/>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Elasticities F51:F58 (Manual inputs rows 279-286). Fix: Read N279:N286 in F51:F58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L102</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual non-energy elasticities can never take effect</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Manual inputs K326:K327; Mitigation K366:M367.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L103</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual SCC reads a path typed on Mitigation, not the Manual inputs block</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H102" s="0"/>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Manual inputs rows 234-240; Mitigation row 17668. Fix: Mitigation row 17668 = 'Manual inputs'!J237 (NSCC) / J240 (GSCC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L104</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name CH4Feebate points to an empty cell</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H103" s="0"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Manual inputs J217 (name CH4Feebate). Fix: Delete the name or point it at the methane fee input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L105</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dashboard industry feebate rates are lost</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F104" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: MTInputs E56:E64 (Dashboard H46:K47).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L106</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual inputs memo swaps the renewables and electricity price elasticities</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Manual inputs K315:N316.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L107</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewable subsidy: start year of the additional subsidy reuses the consumer-subsidy phase-out year</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F106" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation E2736 (policy E9052) = row 270 = MTInputs F132 (YearConsSubPha).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L108</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cost of renewable subsidies counts the base subsidy twice, ignores the hydro switch and omits biomass</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 7883-7889 (policy +6316).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L109</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capex decline options Low and Vhigh have no wind and solar series</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: fallback implemented as planned and accepted (user 2026-10-19); the real Low and Vhigh series are still missing (data gap). Where: Mitigation rows 3038-3046; Power rows 303-330. Fix: Add the Low and Vhigh series to the Power tab, or map the options to the old series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L110</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power revenue rebate counts VAT that was never collected</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 3615, 3644, 3663, 7874, 7735 (policy +6316 / +6316).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L111</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual electricity excise revenue counts the whole excise, also where the price does not include it</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F110" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 3602, 3631, 3660, 7871, 7748.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L112</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Policy copies of the shadow-price rows read the baseline carbon price in the regulation term</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F111" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): the switch still reads $D$2369, which is the same formula as the policy switch (both from G259). Where: Mitigation rows 8693-8704 (policy copies of 2377-2388).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L113</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power switches tested for the exact "Yes" (was issue I58)</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation G261 (PowerRebates), row 3150 (RenewableSubsidyHydro), F201 (AdditionalExcise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L114</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewable subsidies: nominal inputs used as real (was issue I55)</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H113" s="0"/>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2734-2735, 2743, 2745 (MTInputs 352-353). Fix: Deflate the nominal inputs (rows 2734-2735) by the CPI index before they enter row 2743, or relabel MTInputs 352-353 as real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L115</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residential gas: current ETS price reads the LPG transport row</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F114" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In progress</t>
+        </is>
+      </c>
+      <c r="G114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed with caveats in legacy 465: changed, but to the wrong row: K2555:AE2555 and the policy copy read K$1735 (existing carbon tax fuel rate, biomass), not K$1715 (ETS, natural gas, residential). Where: Mitigation row 2555 (policy 8871). Fix: Point row 2555 (and policy 8871) at the residential gas ETS row 1715.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L116</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Services gasoline and diesel income elasticities: step-change column reads the wrong rows</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H115" s="0"/>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Elasticities H53, H54. Fix: Point H53 and H54 at rows 169 and 170.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L117</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfers multiplier (TRNS): estimated lag-0 table read two rows off</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H116" s="0"/>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Multipliers D44. Fix: Read D$1220:D$1418 in D44, as E44:O44.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L118</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual power investment: the need net of manual investment is never used</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F117" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation row 4108.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L119</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NDC year adjustment applied twice for BAU targets and never for Fixed or Historical</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H118" s="0"/>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18399, 18407-18412, 18426-18428, 18443-18445. Fix: Drop the adjustment, or apply it once and to all types (compare in the target year).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L120</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NDC index rows: unconditional and conditional ratios inverted against the average</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H119" s="0"/>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18482-18484. Fix: Use target / start-year emissions in rows 18482-18483, as 18484.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L121</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Historical NDC: the target "level" is the emissions cut</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F120" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H120" s="0"/>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18443-18445. Fix: Return F18437 - F18440 x adj (the level), as the Fixed block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L122</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intensity NDC incl. LULUCF adds a blank cell instead of LULUCF emissions</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H121" s="0"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18461-18462. Fix: Add I18450 (LULUCF) instead of J18450 (non-CO2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L123</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intensity NDC: reference-year GDP read from a fixed cell</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H122" s="0"/>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 18451. Fix: None: not reproduced in the .xlsb (G470 already reads the reference year).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L124</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Producer subsidy: the residential gas block reads the oil subsidy</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): K2547:N2547 and the policy copy now read row 826 (the L82 change). Where: Mitigation row 2547 (N2547).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L125</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Producer subsidy: other oil products add a per-liter value to a per-barrel price</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22): exactly the planned fix. Where: Mitigation row 2685 (N2685).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L126</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power: fuel price for power averages later years</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 3155-3163 (A18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L127</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power: levelised variable cost reads the variable cost to 2041</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H126" s="0"/>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 3439-3447 (D9). Fix: Keep the levelised variable cost (rows 3439-3447) on input-driven costs only; if an ETS price becomes endogenous, levelise the announced price path instead of the solved one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L128</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Net revenue report rows read the next year</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved</t>
+        </is>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPAT team (465)</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in legacy 465 (checked cell by cell, 2026-10-22). Where: Mitigation rows 6238, 6243 (policy 12554, 12559).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L129</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baseline renewable subsidy counted twice</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (Medium)</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H128" s="0"/>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 2785-2788, 2947-2951, 7883-7886 (against 2743, 2745). Fix: In rows 2785-2788, 2947-2951 and 7883-7886 drop the + L2743 term (L2745 already includes it); policy rows the same (+6,316).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L130</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intensity NDC: conditional and unconditional rows use different base years</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H129" s="0"/>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 18455-18456. Fix: F18456: apply the cut to the reference-year intensity F18453, as F18455 does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L131</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codes: one output code on rows with different contents</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H130" s="0"/>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 466, 2442, 16170 (gdp.pre.lvl); 7722, 7742, 7985 (sub.new.usd); 7638-13962 (rev.ctr.coa). Fix: Give each row its own code (e.g. gdp.pre.ln, gdp.pre.mn; sub.new.usd only on its own subtotal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L132</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codes: capitals and empty tokens</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H131" s="0"/>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 7606, 13922 (oc.tot.); em.pm2.All.&lt;sector&gt; rows. Fix: Write the codes in lower case and with a scenario number: em.pm2.all.&lt;sector&gt;, nox.tot.&lt;n&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L133</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codes: nox.tot holds N2O, oc.tot. holds NOx</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H132" s="0"/>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 7606, 13922 and the GHG total rows (nox.tot). Fix: Rename the N2O total n2o.tot and the NOx forcing row nox.tot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L134</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Price-increase units: other oil products "$/bbn", default "$/liter" for other oil products and biomass</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">465</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-23</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H133" s="0"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: MTInputs rows 182-183 (columns E and G); Mitigation I177, I180. Fix: Label the price-increase units USD/bbl (other oil products) and USD/GJ (biomass) in columns E and G of MTInputs rows 182-183.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N1</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Methane intensity decline of agriculture and waste computed but not applied</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F134" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H134" s="0"/>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation rows 6203, 6206, 6212.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N2</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other oil products: new ETS left out of the new-policy total, VAT factor on a blank row</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H135" s="0"/>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Mitigation row 2698.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Targeted transfer capped at 10 points, not the decile's population share</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F136" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H136" s="0"/>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution R2562:Z2562.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basket uses decile 1's elasticity adjustment and exemption test</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H137" s="0"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution C.V, C.VI (e.g. Q1607).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D3</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current spending tests the ASPIRE flag of the targeted transfer</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F138" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H138" s="0"/>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution Q2633.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D4</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public investment and current spending vanish with the transfer settings</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H139" s="0"/>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 2701-2707.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D5</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Targeted exemption capped by all revenue; urban and rural not per capita</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F140" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H140" s="0"/>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution Q2749.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D6</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urban and rural compensation shares on overall weights</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H141" s="0"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution Q3259, Q3263.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D7</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deadweight loss in mixed units</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F142" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H142" s="0"/>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 859-883.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D8</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analysis year and statistic read MTInputs column D</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H143" s="0"/>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: MTOutputs rows 1001-1002.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D9</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rural rows labelled Urban; fuel code oil vs oop</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H144" s="0"/>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution H2417, H2422 (456 numbering; DeepDive cites 2416, 2421): '... - Urban Sample' on rows computed from the rural rows 2402, 2407, 2412; C.II row 746 code 'oil' against price rows 774 and 804 'oop'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D10</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASPIRE transfer pays out more than the revenue</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H145" s="0"/>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2629 (-&gt; 2697-2699).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D11</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASPIRE program without country data: the transfer vanishes</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F146" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H146" s="0"/>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2617, I213.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D12</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASPIRE branch skips the median flag and the zero-coverage test</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F147" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H147" s="0"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2697.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D13</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public investment and current spending use the targeted-transfer median flag</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H148" s="0"/>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 2701-2707.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D14</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poverty targeting: share receiving ignores targeting, coverage and leakage</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F149" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H149" s="0"/>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2679.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D15</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poverty targeting: urban and rural pay out about half of the funds</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F150" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H150" s="0"/>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 2650-2674.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D16</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poverty share x 10 assumes deciles of 10%</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H151" s="0"/>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2649.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D17</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASPIRE values converted without a PPP factor</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F152" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H152" s="0"/>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2618, I220-I223.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D18</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horizontal p25/p75 effects inflated</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H153" s="0"/>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 3188-3206.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D19</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horizontal "chosen statistic" recycling divides by median consumption</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F154" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H154" s="0"/>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 3193, 3201, 3209.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D20</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decile brackets always divided by 1000</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F155" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H155" s="0"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 2774.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D21</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decile bracket labels unusable</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F156" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H156" s="0"/>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 2775-2784.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D22</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sector table "ordered by demand" sorts each column independently</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F157" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H157" s="0"/>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 3300-3310.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D23</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ordered sector tables show 11 of 12 sectors</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F158" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H158" s="0"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 3300-3323.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D24</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemicals and power missing from the CPAT-sector table</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F159" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H159" s="0"/>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 3285-3296.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D25</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chart 19 labels ranked separately from their values; ties</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F160" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H160" s="0"/>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution row 3313.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D26</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass-through coefficients one row off</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F161" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H161" s="0"/>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution G659:BR659.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D27</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTOutputs outpriin labels do not match their values</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F162" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H162" s="0"/>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: MTOutputs K1048:L1058.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D28</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTOutputs codes without a dot</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F163" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H163" s="0"/>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: MTOutputs E1006, E1013.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D29</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTOutputs ppic.fuel empty</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F164" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H164" s="0"/>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: MTOutputs K1046.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D30</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lorenz equality line in 10% steps</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H165" s="0"/>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution rows 2455-2457, 3109.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D31</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Absolute overall rows carry wrong codes</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456</t>
+        </is>
+      </c>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 (Low)</t>
+        </is>
+      </c>
+      <c r="F166" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="G166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen (CPAT-AI)</t>
+        </is>
+      </c>
+      <c r="H166" s="0"/>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open in legacy 465 (not marked fixed by the CPAT team). Where: Distribution L3036:L3043.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I166"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
